--- a/data/trans_orig/P36BPD12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen frutos secos a la semana en 2023</t>
+          <t>Población según el número de veces que consumen frutos secos a la semana en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114044</t>
+          <t>117670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158724</t>
+          <t>160057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130847</t>
+          <t>131236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160545</t>
+          <t>160870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>258742</t>
+          <t>256581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309283</t>
+          <t>309499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98868</t>
+          <t>99944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143634</t>
+          <t>141121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99919</t>
+          <t>101010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127953</t>
+          <t>128830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207243</t>
+          <t>209616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258365</t>
+          <t>261838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39815</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72621</t>
+          <t>72778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39605</t>
+          <t>39005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>67824</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108424</t>
+          <t>105678</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171194</t>
+          <t>172490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227907</t>
+          <t>229092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195334</t>
+          <t>193917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237534</t>
+          <t>234064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379886</t>
+          <t>377988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450137</t>
+          <t>450792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>228765</t>
+          <t>225191</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>287632</t>
+          <t>285732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>224704</t>
+          <t>225318</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>267216</t>
+          <t>265445</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>465191</t>
+          <t>462914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>538537</t>
+          <t>537401</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87224</t>
+          <t>87816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>42405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91328</t>
+          <t>94369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145269</t>
+          <t>144867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83289</t>
+          <t>83444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115122</t>
+          <t>116011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>156040</t>
+          <t>156265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186772</t>
+          <t>187193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>246683</t>
+          <t>246921</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>293966</t>
+          <t>293355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123413</t>
+          <t>123926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157318</t>
+          <t>157791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98594</t>
+          <t>97602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128915</t>
+          <t>127683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229515</t>
+          <t>228967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276824</t>
+          <t>276655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59015</t>
+          <t>58625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87856</t>
+          <t>87727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74040</t>
+          <t>75649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>118215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156031</t>
+          <t>154954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92327</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132838</t>
+          <t>133033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102609</t>
+          <t>100043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199444</t>
+          <t>203158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>195417</t>
+          <t>198329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311002</t>
+          <t>315309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57674</t>
+          <t>57758</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92488</t>
+          <t>94145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51050</t>
+          <t>52325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109350</t>
+          <t>112400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>114618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189170</t>
+          <t>191627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>107241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151551</t>
+          <t>155240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169393</t>
+          <t>167830</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>315301</t>
+          <t>319571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298561</t>
+          <t>294798</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>488548</t>
+          <t>470417</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40496</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52630</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75995</t>
+          <t>75394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>124535</t>
+          <t>125331</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>144093</t>
+          <t>144370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>152422</t>
+          <t>153221</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>168889</t>
+          <t>170002</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>284100</t>
+          <t>284958</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>309427</t>
+          <t>309435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>32336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68727</t>
+          <t>69193</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>95777</t>
+          <t>95854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121268</t>
+          <t>121930</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>147530</t>
+          <t>147920</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>196637</t>
+          <t>199380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>235744</t>
+          <t>236493</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131889</t>
+          <t>130179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110413</t>
+          <t>108088</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>191456</t>
+          <t>190595</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>230035</t>
+          <t>230183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60246</t>
+          <t>60275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>86747</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83504</t>
+          <t>85068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114202</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>250783</t>
+          <t>251862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>311153</t>
+          <t>313115</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132371</t>
+          <t>123916</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>342203</t>
+          <t>343188</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>335244</t>
+          <t>332068</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>633225</t>
+          <t>632722</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>149339</t>
+          <t>147494</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>200924</t>
+          <t>198608</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>230199</t>
+          <t>226740</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>613544</t>
+          <t>611848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>397274</t>
+          <t>397384</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>923525</t>
+          <t>895723</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>144655</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195931</t>
+          <t>197139</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102147</t>
+          <t>102125</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>286294</t>
+          <t>287432</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>224064</t>
+          <t>235392</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>455545</t>
+          <t>456427</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178112</t>
+          <t>178745</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159363</t>
+          <t>161300</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>199809</t>
+          <t>199922</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>185603</t>
+          <t>194619</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>371073</t>
+          <t>370560</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>586482</t>
+          <t>583630</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>816240</t>
+          <t>812491</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>412982</t>
+          <t>413409</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>461769</t>
+          <t>462444</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1015927</t>
+          <t>1013652</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1335997</t>
+          <t>1309788</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54017</t>
+          <t>54793</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>171866</t>
+          <t>173193</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>84460</t>
+          <t>83995</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>119956</t>
+          <t>119200</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>139160</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>269972</t>
+          <t>273984</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>842879</t>
+          <t>819866</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1170384</t>
+          <t>1169226</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1012179</t>
+          <t>1033252</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1388886</t>
+          <t>1388564</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2040403</t>
+          <t>2067202</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2524077</t>
+          <t>2531120</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1542506</t>
+          <t>1545399</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2070194</t>
+          <t>2122918</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1481323</t>
+          <t>1494700</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2010684</t>
+          <t>2023782</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3083933</t>
+          <t>3069504</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3845222</t>
+          <t>3828642</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>548334</t>
+          <t>510350</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>769799</t>
+          <t>766420</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>613826</t>
+          <t>616878</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>912251</t>
+          <t>920378</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1251466</t>
+          <t>1249143</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1617410</t>
+          <t>1631000</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>137767</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117670</t>
+          <t>119313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160057</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>144560</t>
+          <t>148954</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131236</t>
+          <t>134178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160870</t>
+          <t>163135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>282770</t>
+          <t>286721</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256581</t>
+          <t>263538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309499</t>
+          <t>310339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119026</t>
+          <t>123792</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99944</t>
+          <t>107923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141121</t>
+          <t>142861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114702</t>
+          <t>133246</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101010</t>
+          <t>118513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128830</t>
+          <t>147991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>233727</t>
+          <t>257039</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209616</t>
+          <t>234128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261838</t>
+          <t>280726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54206</t>
+          <t>57286</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>43354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72778</t>
+          <t>72392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30374</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39005</t>
+          <t>43713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>84580</t>
+          <t>91146</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67824</t>
+          <t>74639</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105678</t>
+          <t>108697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>199212</t>
+          <t>200924</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172490</t>
+          <t>174375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229092</t>
+          <t>230685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>215386</t>
+          <t>228867</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193917</t>
+          <t>207751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234064</t>
+          <t>250368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>414597</t>
+          <t>429791</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>377988</t>
+          <t>397096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450792</t>
+          <t>465640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>267048</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225191</t>
+          <t>240219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>285732</t>
+          <t>295547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>245109</t>
+          <t>258961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>225318</t>
+          <t>237915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>265445</t>
+          <t>280111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>501374</t>
+          <t>526009</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>462914</t>
+          <t>490516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>537401</t>
+          <t>562856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,3%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42136</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87816</t>
+          <t>84621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67466</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>116520</t>
+          <t>120421</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94369</t>
+          <t>97488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144867</t>
+          <t>149826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529726</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1032491</t>
+          <t>1076221</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1032491</t>
+          <t>1076221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1032491</t>
+          <t>1076221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98918</t>
+          <t>98280</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83444</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116011</t>
+          <t>115138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>171215</t>
+          <t>176703</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>156265</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187193</t>
+          <t>192531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>270132</t>
+          <t>274984</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>246921</t>
+          <t>253624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>293355</t>
+          <t>297301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>140159</t>
+          <t>140676</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123926</t>
+          <t>124016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157791</t>
+          <t>157187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>112651</t>
+          <t>112450</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97602</t>
+          <t>98613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127683</t>
+          <t>126187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>252810</t>
+          <t>253126</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228967</t>
+          <t>231138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276655</t>
+          <t>275774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>73589</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58625</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87727</t>
+          <t>89152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62498</t>
+          <t>64446</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51424</t>
+          <t>53404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75649</t>
+          <t>76393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>135961</t>
+          <t>138035</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118215</t>
+          <t>120275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154954</t>
+          <t>156874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312540</t>
+          <t>312545</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312540</t>
+          <t>312545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312540</t>
+          <t>312545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>346363</t>
+          <t>353599</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>346363</t>
+          <t>353599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>346363</t>
+          <t>353599</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>658903</t>
+          <t>666145</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>658903</t>
+          <t>666145</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>658903</t>
+          <t>666145</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>110373</t>
+          <t>128210</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>106003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133033</t>
+          <t>157315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>158043</t>
+          <t>175983</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100043</t>
+          <t>156599</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203158</t>
+          <t>197801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>268415</t>
+          <t>304192</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198329</t>
+          <t>272691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315309</t>
+          <t>335085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73851</t>
+          <t>82870</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>63365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94145</t>
+          <t>103968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84723</t>
+          <t>94626</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>79038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112400</t>
+          <t>112795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>158574</t>
+          <t>177497</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114618</t>
+          <t>154064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191627</t>
+          <t>205161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>128333</t>
+          <t>162065</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107241</t>
+          <t>135120</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155240</t>
+          <t>187783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>231833</t>
+          <t>150182</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>167830</t>
+          <t>128883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>319571</t>
+          <t>169939</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>360165</t>
+          <t>312247</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>294798</t>
+          <t>281870</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>470417</t>
+          <t>346812</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>474599</t>
+          <t>420791</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>474599</t>
+          <t>420791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>474599</t>
+          <t>420791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>787155</t>
+          <t>793936</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>787155</t>
+          <t>793936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>787155</t>
+          <t>793936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>34321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>26943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>47306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39884</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>63566</t>
+          <t>70531</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>57421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75394</t>
+          <t>83349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>135438</t>
+          <t>157821</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125331</t>
+          <t>145571</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>144370</t>
+          <t>167297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>161888</t>
+          <t>175686</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>166381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170002</t>
+          <t>183959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>297326</t>
+          <t>333507</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>284958</t>
+          <t>317924</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>309435</t>
+          <t>347252</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19745</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>177394</t>
+          <t>204193</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177394</t>
+          <t>204193</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177394</t>
+          <t>204193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>385668</t>
+          <t>431016</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>385668</t>
+          <t>431016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>385668</t>
+          <t>431016</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>85021</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>71844</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>95854</t>
+          <t>98709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>135154</t>
+          <t>137065</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121930</t>
+          <t>123626</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>147920</t>
+          <t>149099</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>216996</t>
+          <t>222085</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>199380</t>
+          <t>202469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>236493</t>
+          <t>241087</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>115550</t>
+          <t>113267</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99333</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130179</t>
+          <t>127262</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>94839</t>
+          <t>96867</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>85028</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108088</t>
+          <t>110306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>210389</t>
+          <t>210134</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190595</t>
+          <t>191821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>230183</t>
+          <t>229363</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>72244</t>
+          <t>72419</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60275</t>
+          <t>59627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>86339</t>
+          <t>86256</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27063</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>22804</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>99307</t>
+          <t>102237</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85068</t>
+          <t>86281</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116106</t>
+          <t>117291</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>280862</t>
+          <t>314907</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>251862</t>
+          <t>285451</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>313115</t>
+          <t>343076</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>252983</t>
+          <t>296651</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>123916</t>
+          <t>270560</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>343188</t>
+          <t>323255</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>533845</t>
+          <t>611558</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>332068</t>
+          <t>570191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>632722</t>
+          <t>650189</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>173045</t>
+          <t>208679</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147494</t>
+          <t>182233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>198608</t>
+          <t>238852</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>383274</t>
+          <t>217321</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>226740</t>
+          <t>194723</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>611848</t>
+          <t>240193</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>556319</t>
+          <t>426000</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>397384</t>
+          <t>392857</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>895723</t>
+          <t>463738</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>169343</t>
+          <t>195019</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>144554</t>
+          <t>166353</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>197139</t>
+          <t>222083</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>212289</t>
+          <t>257347</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102125</t>
+          <t>233879</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>287432</t>
+          <t>281919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>381632</t>
+          <t>452366</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>235392</t>
+          <t>417087</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>456427</t>
+          <t>487659</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>848545</t>
+          <t>771319</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>848545</t>
+          <t>771319</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>848545</t>
+          <t>771319</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1471795</t>
+          <t>1489924</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1471795</t>
+          <t>1489924</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1471795</t>
+          <t>1489924</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>125831</t>
+          <t>148492</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>128053</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178745</t>
+          <t>174542</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>179665</t>
+          <t>211280</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>161300</t>
+          <t>188266</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>199922</t>
+          <t>235726</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>305497</t>
+          <t>359772</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>194619</t>
+          <t>329880</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>370560</t>
+          <t>392059</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>681559</t>
+          <t>509260</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>583630</t>
+          <t>479479</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>812491</t>
+          <t>537731</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>437454</t>
+          <t>509527</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>413409</t>
+          <t>483747</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>462444</t>
+          <t>534619</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1119014</t>
+          <t>1018787</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1013652</t>
+          <t>980147</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1054661</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>121330</t>
+          <t>140320</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>117506</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>173193</t>
+          <t>164947</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>100611</t>
+          <t>110525</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>83995</t>
+          <t>93785</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>119200</t>
+          <t>129848</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>221941</t>
+          <t>250845</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>139160</t>
+          <t>221654</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273984</t>
+          <t>281703</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1066388</t>
+          <t>1147921</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>819866</t>
+          <t>1086313</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1169226</t>
+          <t>1208431</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1289430</t>
+          <t>1411713</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1033252</t>
+          <t>1357625</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1388564</t>
+          <t>1462032</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2355818</t>
+          <t>2559634</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2067202</t>
+          <t>2479688</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2531120</t>
+          <t>2639314</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1694895</t>
+          <t>1603414</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1545399</t>
+          <t>1542257</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2122918</t>
+          <t>1668941</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1634639</t>
+          <t>1598684</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1494700</t>
+          <t>1548051</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2023782</t>
+          <t>1656664</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3329534</t>
+          <t>3202098</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3069504</t>
+          <t>3120985</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3828642</t>
+          <t>3278085</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>691780</t>
+          <t>774504</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>510350</t>
+          <t>714044</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>766420</t>
+          <t>827131</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>733102</t>
+          <t>719773</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>616878</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>920378</t>
+          <t>763996</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1494277</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1249143</t>
+          <t>1424424</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1631000</t>
+          <t>1566402</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
